--- a/bancos/manual/desc_subfuncao.xlsx
+++ b/bancos/manual/desc_subfuncao.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29301"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="S:\2.Programação e Normas\2023\PPAG 2023 e LOA 2023\Tabelas de Apoio - geração dos volumes 2023\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\x1569275\CAMG\Splor Geral - @dcppn\00- DCPPN 2027\PPAG e LOA 2027\Dados para Volumes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_EC26C91BF040C27A188F7B201667BB70E4AC1C1E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="15345" windowHeight="3645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="15345" windowHeight="3645"/>
   </bookViews>
   <sheets>
     <sheet name="Plan1" sheetId="1" r:id="rId1"/>
@@ -24,6 +23,17 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
@@ -370,8 +380,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -681,15 +691,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B111"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.28515625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="53.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -697,7 +707,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>31</v>
       </c>
@@ -705,7 +715,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>32</v>
       </c>
@@ -713,7 +723,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>61</v>
       </c>
@@ -721,7 +731,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>62</v>
       </c>
@@ -729,7 +739,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>91</v>
       </c>
@@ -737,7 +747,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>92</v>
       </c>
@@ -745,7 +755,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>121</v>
       </c>
@@ -753,7 +763,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>122</v>
       </c>
@@ -761,7 +771,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>123</v>
       </c>
@@ -769,7 +779,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>124</v>
       </c>
@@ -777,7 +787,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:2">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>125</v>
       </c>
@@ -785,7 +795,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:2">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>126</v>
       </c>
@@ -793,7 +803,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:2">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>127</v>
       </c>
@@ -801,7 +811,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="15" spans="1:2">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>128</v>
       </c>
@@ -809,7 +819,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:2">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>129</v>
       </c>
@@ -817,7 +827,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="17" spans="1:2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>130</v>
       </c>
@@ -825,7 +835,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="18" spans="1:2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>131</v>
       </c>
@@ -833,7 +843,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="19" spans="1:2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>151</v>
       </c>
@@ -841,7 +851,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="20" spans="1:2">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>152</v>
       </c>
@@ -849,7 +859,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="21" spans="1:2">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>153</v>
       </c>
@@ -857,7 +867,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="22" spans="1:2">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>181</v>
       </c>
@@ -865,7 +875,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="23" spans="1:2">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>182</v>
       </c>
@@ -873,7 +883,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="24" spans="1:2">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>183</v>
       </c>
@@ -881,7 +891,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="25" spans="1:2">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>211</v>
       </c>
@@ -889,7 +899,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="26" spans="1:2">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>212</v>
       </c>
@@ -897,7 +907,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="27" spans="1:2">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>241</v>
       </c>
@@ -905,7 +915,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="28" spans="1:2">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>242</v>
       </c>
@@ -913,7 +923,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="29" spans="1:2">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>243</v>
       </c>
@@ -921,7 +931,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="30" spans="1:2">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>244</v>
       </c>
@@ -929,7 +939,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="31" spans="1:2">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>271</v>
       </c>
@@ -937,7 +947,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="32" spans="1:2">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>272</v>
       </c>
@@ -945,7 +955,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="33" spans="1:2">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>273</v>
       </c>
@@ -953,7 +963,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="34" spans="1:2">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>274</v>
       </c>
@@ -961,7 +971,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="35" spans="1:2">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>301</v>
       </c>
@@ -969,7 +979,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="36" spans="1:2">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>302</v>
       </c>
@@ -977,7 +987,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="37" spans="1:2">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>303</v>
       </c>
@@ -985,7 +995,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="38" spans="1:2">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>304</v>
       </c>
@@ -993,7 +1003,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="39" spans="1:2">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>305</v>
       </c>
@@ -1001,7 +1011,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="40" spans="1:2">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>306</v>
       </c>
@@ -1009,7 +1019,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="41" spans="1:2">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>331</v>
       </c>
@@ -1017,7 +1027,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="42" spans="1:2">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>332</v>
       </c>
@@ -1025,7 +1035,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="43" spans="1:2">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>333</v>
       </c>
@@ -1033,7 +1043,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="44" spans="1:2">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>334</v>
       </c>
@@ -1041,7 +1051,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="45" spans="1:2">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>361</v>
       </c>
@@ -1049,7 +1059,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="46" spans="1:2">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>362</v>
       </c>
@@ -1057,7 +1067,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="47" spans="1:2">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>363</v>
       </c>
@@ -1065,7 +1075,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="48" spans="1:2">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>364</v>
       </c>
@@ -1073,7 +1083,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="49" spans="1:2">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>365</v>
       </c>
@@ -1081,7 +1091,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="50" spans="1:2">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>366</v>
       </c>
@@ -1089,7 +1099,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="51" spans="1:2">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>367</v>
       </c>
@@ -1097,7 +1107,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="52" spans="1:2">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>368</v>
       </c>
@@ -1105,7 +1115,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="53" spans="1:2">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>391</v>
       </c>
@@ -1113,7 +1123,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="54" spans="1:2">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>392</v>
       </c>
@@ -1121,7 +1131,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="55" spans="1:2">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>421</v>
       </c>
@@ -1129,7 +1139,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="56" spans="1:2">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>422</v>
       </c>
@@ -1137,7 +1147,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="57" spans="1:2">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>423</v>
       </c>
@@ -1145,7 +1155,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="58" spans="1:2">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>451</v>
       </c>
@@ -1153,7 +1163,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="59" spans="1:2">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>452</v>
       </c>
@@ -1161,7 +1171,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="60" spans="1:2">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>453</v>
       </c>
@@ -1169,7 +1179,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="61" spans="1:2">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>481</v>
       </c>
@@ -1177,7 +1187,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="62" spans="1:2">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>482</v>
       </c>
@@ -1185,7 +1195,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="63" spans="1:2">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>511</v>
       </c>
@@ -1193,7 +1203,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="64" spans="1:2">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>512</v>
       </c>
@@ -1201,7 +1211,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="65" spans="1:2">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>541</v>
       </c>
@@ -1209,7 +1219,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="66" spans="1:2">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>542</v>
       </c>
@@ -1217,7 +1227,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="67" spans="1:2">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>543</v>
       </c>
@@ -1225,7 +1235,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="68" spans="1:2">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>544</v>
       </c>
@@ -1233,7 +1243,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="69" spans="1:2">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>545</v>
       </c>
@@ -1241,7 +1251,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="70" spans="1:2">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>571</v>
       </c>
@@ -1249,7 +1259,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="71" spans="1:2">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>572</v>
       </c>
@@ -1257,7 +1267,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="72" spans="1:2">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>573</v>
       </c>
@@ -1265,7 +1275,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="73" spans="1:2">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>605</v>
       </c>
@@ -1273,7 +1283,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="74" spans="1:2">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>606</v>
       </c>
@@ -1281,7 +1291,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="75" spans="1:2">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>607</v>
       </c>
@@ -1289,7 +1299,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="76" spans="1:2">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>608</v>
       </c>
@@ -1297,7 +1307,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="77" spans="1:2">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>609</v>
       </c>
@@ -1305,7 +1315,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="78" spans="1:2">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>631</v>
       </c>
@@ -1313,7 +1323,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="79" spans="1:2">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>632</v>
       </c>
@@ -1321,7 +1331,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="80" spans="1:2">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>661</v>
       </c>
@@ -1329,7 +1339,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="81" spans="1:2">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>662</v>
       </c>
@@ -1337,7 +1347,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="82" spans="1:2">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>663</v>
       </c>
@@ -1345,7 +1355,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="83" spans="1:2">
+    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>664</v>
       </c>
@@ -1353,7 +1363,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="84" spans="1:2">
+    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>665</v>
       </c>
@@ -1361,7 +1371,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="85" spans="1:2">
+    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>691</v>
       </c>
@@ -1369,7 +1379,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="86" spans="1:2">
+    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>692</v>
       </c>
@@ -1377,7 +1387,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="87" spans="1:2">
+    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>693</v>
       </c>
@@ -1385,7 +1395,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="88" spans="1:2">
+    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>694</v>
       </c>
@@ -1393,7 +1403,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="89" spans="1:2">
+    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>695</v>
       </c>
@@ -1401,7 +1411,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="90" spans="1:2">
+    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>721</v>
       </c>
@@ -1409,7 +1419,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="91" spans="1:2">
+    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>722</v>
       </c>
@@ -1417,7 +1427,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="92" spans="1:2">
+    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A92">
         <v>751</v>
       </c>
@@ -1425,7 +1435,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="93" spans="1:2">
+    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A93">
         <v>752</v>
       </c>
@@ -1433,7 +1443,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="94" spans="1:2">
+    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A94">
         <v>753</v>
       </c>
@@ -1441,7 +1451,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="95" spans="1:2">
+    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A95">
         <v>754</v>
       </c>
@@ -1449,7 +1459,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="96" spans="1:2">
+    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A96">
         <v>781</v>
       </c>
@@ -1457,7 +1467,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="97" spans="1:2">
+    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A97">
         <v>782</v>
       </c>
@@ -1465,7 +1475,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="98" spans="1:2">
+    <row r="98" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A98">
         <v>783</v>
       </c>
@@ -1473,7 +1483,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="99" spans="1:2">
+    <row r="99" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A99">
         <v>784</v>
       </c>
@@ -1481,7 +1491,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="100" spans="1:2">
+    <row r="100" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A100">
         <v>785</v>
       </c>
@@ -1489,7 +1499,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="101" spans="1:2">
+    <row r="101" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A101">
         <v>811</v>
       </c>
@@ -1497,7 +1507,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="102" spans="1:2">
+    <row r="102" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A102">
         <v>812</v>
       </c>
@@ -1505,7 +1515,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="103" spans="1:2">
+    <row r="103" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A103">
         <v>813</v>
       </c>
@@ -1513,7 +1523,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="104" spans="1:2">
+    <row r="104" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A104">
         <v>841</v>
       </c>
@@ -1521,7 +1531,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="105" spans="1:2">
+    <row r="105" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A105">
         <v>842</v>
       </c>
@@ -1529,7 +1539,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="106" spans="1:2">
+    <row r="106" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A106">
         <v>843</v>
       </c>
@@ -1537,7 +1547,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="107" spans="1:2">
+    <row r="107" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A107">
         <v>844</v>
       </c>
@@ -1545,7 +1555,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="108" spans="1:2">
+    <row r="108" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A108">
         <v>845</v>
       </c>
@@ -1553,7 +1563,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="109" spans="1:2">
+    <row r="109" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A109">
         <v>846</v>
       </c>
@@ -1561,7 +1571,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="110" spans="1:2">
+    <row r="110" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A110">
         <v>847</v>
       </c>
@@ -1569,7 +1579,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="111" spans="1:2">
+    <row r="111" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A111">
         <v>999</v>
       </c>
@@ -1584,6 +1594,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="b91e7f20-fe0a-487d-91a9-605ac1c64acf" xsi:nil="true"/>
@@ -1601,18 +1620,9 @@
 </p:properties>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100B08D58FADB61F04EBBB4F355C06EFBED" ma:contentTypeVersion="19" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="7797dc5feb179b4da55a9ebddd321181">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="6f4338ef-addb-4c87-aefe-1895241b335f" xmlns:ns3="b91e7f20-fe0a-487d-91a9-605ac1c64acf" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="90078f443198b6d5c0fd169535a443b9" ns2:_="" ns3:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100B08D58FADB61F04EBBB4F355C06EFBED" ma:contentTypeVersion="19" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="b1e0f6055e0e9a4b9e75d6c71ee7de91">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="6f4338ef-addb-4c87-aefe-1895241b335f" xmlns:ns3="b91e7f20-fe0a-487d-91a9-605ac1c64acf" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b43930f3490e4d4da1ab3f8da7df6f51" ns2:_="" ns3:_="">
     <xsd:import namespace="6f4338ef-addb-4c87-aefe-1895241b335f"/>
     <xsd:import namespace="b91e7f20-fe0a-487d-91a9-605ac1c64acf"/>
     <xsd:element name="properties">
@@ -1872,13 +1882,45 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8A8736FE-6255-4FD1-8C32-47721AF24FF0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7EAA5A96-60E0-4C51-8584-699CBD88CF93}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7EAA5A96-60E0-4C51-8584-699CBD88CF93}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8A8736FE-6255-4FD1-8C32-47721AF24FF0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="6f4338ef-addb-4c87-aefe-1895241b335f"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="b91e7f20-fe0a-487d-91a9-605ac1c64acf"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{60504B4E-13D0-4AB7-834B-C4A00410F540}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7F771552-5651-4207-9E9D-C4823C65627F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="6f4338ef-addb-4c87-aefe-1895241b335f"/>
+    <ds:schemaRef ds:uri="b91e7f20-fe0a-487d-91a9-605ac1c64acf"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>